--- a/PCB/四旋翼无人机无刷驱动/无刷电机驱动BOOM.xlsx
+++ b/PCB/四旋翼无人机无刷驱动/无刷电机驱动BOOM.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027DC9DB-C18B-4BB7-BEE9-8EB1960242FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="BOM_无刷电机驱动_原理图_2025-11-29" state="visible" r:id="rId4"/>
+    <sheet name="BOM_无刷电机驱动_原理图_2025-11-29" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -337,22 +341,48 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -367,11 +397,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -707,11 +740,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="20" customWidth="1"/>
+    <col min="1" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -750,7 +785,7 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -782,7 +817,7 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>3</v>
       </c>
       <c r="C3" t="s">
@@ -814,7 +849,7 @@
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -846,7 +881,7 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
       <c r="C5" t="s">
@@ -878,7 +913,7 @@
       <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -910,7 +945,7 @@
       <c r="A7" t="s">
         <v>34</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -942,7 +977,7 @@
       <c r="A8" t="s">
         <v>38</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>8</v>
       </c>
       <c r="C8" t="s">
@@ -974,7 +1009,7 @@
       <c r="A9" t="s">
         <v>42</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>12</v>
       </c>
       <c r="C9" t="s">
@@ -1006,7 +1041,7 @@
       <c r="A10" t="s">
         <v>45</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>6</v>
       </c>
       <c r="C10" t="s">
@@ -1038,7 +1073,7 @@
       <c r="A11" t="s">
         <v>48</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>3</v>
       </c>
       <c r="C11" t="s">
@@ -1070,7 +1105,7 @@
       <c r="A12" t="s">
         <v>55</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -1102,7 +1137,7 @@
       <c r="A13" t="s">
         <v>58</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" t="s">
@@ -1134,7 +1169,7 @@
       <c r="A14" t="s">
         <v>61</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" t="s">
@@ -1166,7 +1201,7 @@
       <c r="A15" t="s">
         <v>64</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>1</v>
       </c>
       <c r="C15" t="s">
@@ -1198,7 +1233,7 @@
       <c r="A16" t="s">
         <v>67</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -1230,7 +1265,7 @@
       <c r="A17" t="s">
         <v>71</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>1</v>
       </c>
       <c r="C17" t="s">
@@ -1262,7 +1297,7 @@
       <c r="A18" t="s">
         <v>77</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>6</v>
       </c>
       <c r="C18" t="s">
@@ -1294,7 +1329,7 @@
       <c r="A19" t="s">
         <v>83</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>1</v>
       </c>
       <c r="C19" t="s">
@@ -1326,7 +1361,7 @@
       <c r="A20" t="s">
         <v>86</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>2</v>
       </c>
       <c r="C20" t="s">
@@ -1358,7 +1393,7 @@
       <c r="A21" t="s">
         <v>92</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>1</v>
       </c>
       <c r="C21" t="s">
@@ -1390,7 +1425,7 @@
       <c r="A22" t="s">
         <v>98</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>1</v>
       </c>
       <c r="C22" t="s">
@@ -1422,7 +1457,7 @@
       <c r="A23" t="s">
         <v>101</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>2</v>
       </c>
       <c r="C23" t="s">
@@ -1450,14 +1485,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>